--- a/Fleet_Team_WO_Follow_Up_10_13_2026_cleaned.xlsx
+++ b/Fleet_Team_WO_Follow_Up_10_13_2026_cleaned.xlsx
@@ -40314,7 +40314,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>fleet_management@mccoys.com</t>
+          <t>John Grimsley</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -41222,7 +41222,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>fleet_management@mccoys.com</t>
+          <t>John Grimsley</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -41283,7 +41283,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>fleet_management@mccoys.com</t>
+          <t>John Grimsley</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -41344,7 +41344,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>fleet_management@mccoys.com</t>
+          <t>John Grimsley</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
